--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_string.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_string.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_string" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6064" uniqueCount="1790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6064" uniqueCount="1793">
   <si>
     <t>id</t>
   </si>
@@ -4048,7 +4053,7 @@
     <t>text35005</t>
   </si>
   <si>
-    <t>是否进行传送</t>
+    <t>是否进行传送?</t>
   </si>
   <si>
     <t>玩家被击杀</t>
@@ -4075,19 +4080,19 @@
     <t>text38001</t>
   </si>
   <si>
-    <t>穿戴4种套装激活额外属性加成！</t>
+    <t>穿戴4种时装获得额外属性加成！</t>
   </si>
   <si>
     <t>text38002</t>
   </si>
   <si>
-    <t>穿戴3种套装激活额外属性加成！</t>
+    <t>穿戴3种时装获得额外属性加成！</t>
   </si>
   <si>
     <t>text38003</t>
   </si>
   <si>
-    <t>穿戴2种套装激活额外属性加成！</t>
+    <t>穿戴2种时装获得额外属性加成！</t>
   </si>
   <si>
     <t>装备首爆文本内容</t>
@@ -4607,11 +4612,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>是否删除角色</t>
     </r>
     <r>
@@ -4628,7 +4628,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>每日仅删除一名</t>
+      <t>每日可删除一名</t>
     </r>
     <r>
       <rPr>
@@ -5346,6 +5346,15 @@
   </si>
   <si>
     <t>复古奇迹1.03H！\n经典5/6/7点，10倍爆率\n月卡版，无累充，无礼包\n一切靠打，大服生态，人气火爆！</t>
+  </si>
+  <si>
+    <t>穿戴4种套装激活额外属性加成！</t>
+  </si>
+  <si>
+    <t>穿戴3种套装激活额外属性加成！</t>
+  </si>
+  <si>
+    <t>穿戴2种套装激活额外属性加成！</t>
   </si>
   <si>
     <t>首爆装备包括可交易的【卓越】武器，防具#首爆获得奖励最高，末爆获得奖励最低#按怪物爆出时间顺序触发奖励#【总计超8888元】可交易钻石奖励，抢到就是赚到！</t>
@@ -51681,7 +51690,7 @@
         <v>20</v>
       </c>
       <c r="Q459" s="5" t="s">
-        <v>1335</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="460" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -51722,7 +51731,7 @@
         <v>20</v>
       </c>
       <c r="Q460" s="5" t="s">
-        <v>1337</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="461" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -51763,7 +51772,7 @@
         <v>20</v>
       </c>
       <c r="Q461" s="5" t="s">
-        <v>1339</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="462" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -51804,7 +51813,7 @@
         <v>20</v>
       </c>
       <c r="Q462" s="1" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="463" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -51886,7 +51895,7 @@
         <v>20</v>
       </c>
       <c r="Q464" s="6" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="465" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -51927,7 +51936,7 @@
         <v>20</v>
       </c>
       <c r="Q465" s="1" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="466" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -51968,7 +51977,7 @@
         <v>20</v>
       </c>
       <c r="Q466" s="1" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="467" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -52015,7 +52024,7 @@
         <v>8</v>
       </c>
       <c r="Q467" s="1" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="R467" s="1" t="s">
         <v>20</v>
@@ -52071,7 +52080,7 @@
         <v>2</v>
       </c>
       <c r="Q468" s="1" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="S468" s="2">
         <v>2000</v>
@@ -52121,7 +52130,7 @@
         <v>2</v>
       </c>
       <c r="Q469" s="1" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="S469" s="2">
         <v>2000</v>
@@ -52171,7 +52180,7 @@
         <v>2</v>
       </c>
       <c r="Q470" s="1" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
       <c r="S470" s="2">
         <v>2000</v>
@@ -52215,7 +52224,7 @@
         <v>20</v>
       </c>
       <c r="Q471" s="1" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="472" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -52256,7 +52265,7 @@
         <v>20</v>
       </c>
       <c r="Q472" s="5" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="473" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -52297,7 +52306,7 @@
         <v>20</v>
       </c>
       <c r="Q473" s="1" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="474" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -52379,7 +52388,7 @@
         <v>20</v>
       </c>
       <c r="Q475" s="5" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="476" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -52420,7 +52429,7 @@
         <v>20</v>
       </c>
       <c r="Q476" s="1" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="477" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -52461,7 +52470,7 @@
         <v>20</v>
       </c>
       <c r="Q477" s="1" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="478" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -52502,7 +52511,7 @@
         <v>20</v>
       </c>
       <c r="Q478" s="1" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="479" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -52543,7 +52552,7 @@
         <v>20</v>
       </c>
       <c r="Q479" s="1" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="480" s="1" customFormat="1" ht="14.25" spans="1:20">
@@ -52625,7 +52634,7 @@
         <v>20</v>
       </c>
       <c r="Q481" s="1" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="482" s="1" customFormat="1" ht="14.25" spans="1:19">
@@ -52672,7 +52681,7 @@
         <v>20</v>
       </c>
       <c r="Q482" s="1" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="483" s="1" customFormat="1" ht="14.25" spans="1:19">
@@ -52766,7 +52775,7 @@
         <v>20</v>
       </c>
       <c r="Q484" s="1" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="485" s="1" customFormat="1" ht="14.25" spans="1:19">
@@ -52813,7 +52822,7 @@
         <v>20</v>
       </c>
       <c r="Q485" s="1" t="s">
-        <v>1751</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="486" s="1" customFormat="1" ht="14.25" spans="1:19">
@@ -52854,7 +52863,7 @@
         <v>20</v>
       </c>
       <c r="Q486" s="1" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="487" s="1" customFormat="1" ht="14.25" spans="1:19">
@@ -52895,7 +52904,7 @@
         <v>20</v>
       </c>
       <c r="Q487" s="5" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="488" s="1" customFormat="1" ht="14.25" spans="1:19">
@@ -52936,7 +52945,7 @@
         <v>20</v>
       </c>
       <c r="Q488" s="5" t="s">
-        <v>1754</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="489" s="1" customFormat="1" ht="14.25" spans="1:19">
@@ -53331,7 +53340,7 @@
         <v>20</v>
       </c>
       <c r="Q496" s="5" t="s">
-        <v>1755</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="497" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53372,7 +53381,7 @@
         <v>20</v>
       </c>
       <c r="Q497" s="5" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="498" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53413,7 +53422,7 @@
         <v>20</v>
       </c>
       <c r="Q498" s="5" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="499" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53454,7 +53463,7 @@
         <v>20</v>
       </c>
       <c r="Q499" s="5" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="500" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53495,7 +53504,7 @@
         <v>20</v>
       </c>
       <c r="Q500" s="5" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="501" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53536,7 +53545,7 @@
         <v>20</v>
       </c>
       <c r="Q501" s="5" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="502" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53577,7 +53586,7 @@
         <v>20</v>
       </c>
       <c r="Q502" s="5" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="503" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53618,7 +53627,7 @@
         <v>20</v>
       </c>
       <c r="Q503" s="5" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="504" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53659,7 +53668,7 @@
         <v>20</v>
       </c>
       <c r="Q504" s="5" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="505" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53700,7 +53709,7 @@
         <v>20</v>
       </c>
       <c r="Q505" s="1" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="506" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53741,7 +53750,7 @@
         <v>20</v>
       </c>
       <c r="Q506" s="1" t="s">
-        <v>1765</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="507" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53782,7 +53791,7 @@
         <v>20</v>
       </c>
       <c r="Q507" s="1" t="s">
-        <v>1766</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="508" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53823,7 +53832,7 @@
         <v>20</v>
       </c>
       <c r="Q508" s="1" t="s">
-        <v>1767</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="509" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53864,7 +53873,7 @@
         <v>20</v>
       </c>
       <c r="Q509" s="1" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="510" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53905,7 +53914,7 @@
         <v>20</v>
       </c>
       <c r="Q510" s="1" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="511" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53946,7 +53955,7 @@
         <v>20</v>
       </c>
       <c r="Q511" s="3" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="512" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -53987,7 +53996,7 @@
         <v>20</v>
       </c>
       <c r="Q512" s="1" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="513" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54110,7 +54119,7 @@
         <v>20</v>
       </c>
       <c r="Q515" s="1" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="516" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -54192,7 +54201,7 @@
         <v>20</v>
       </c>
       <c r="Q517" s="1" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="518" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54233,7 +54242,7 @@
         <v>20</v>
       </c>
       <c r="Q518" s="1" t="s">
-        <v>1774</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="519" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54274,7 +54283,7 @@
         <v>20</v>
       </c>
       <c r="Q519" s="1" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="520" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54356,7 +54365,7 @@
         <v>20</v>
       </c>
       <c r="Q521" s="1" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="522" s="1" customFormat="1" spans="1:17">
@@ -54397,7 +54406,7 @@
         <v>20</v>
       </c>
       <c r="Q522" s="13" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="523" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54438,7 +54447,7 @@
         <v>20</v>
       </c>
       <c r="Q523" s="1" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="524" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54479,7 +54488,7 @@
         <v>20</v>
       </c>
       <c r="Q524" s="1" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="525" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54520,7 +54529,7 @@
         <v>20</v>
       </c>
       <c r="Q525" s="1" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="526" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54561,7 +54570,7 @@
         <v>20</v>
       </c>
       <c r="Q526" s="1" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="527" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54602,7 +54611,7 @@
         <v>20</v>
       </c>
       <c r="Q527" s="1" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="528" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54643,7 +54652,7 @@
         <v>20</v>
       </c>
       <c r="Q528" s="1" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="529" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54684,7 +54693,7 @@
         <v>20</v>
       </c>
       <c r="Q529" s="1" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="530" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54725,7 +54734,7 @@
         <v>20</v>
       </c>
       <c r="Q530" s="1" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="531" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54766,7 +54775,7 @@
         <v>20</v>
       </c>
       <c r="Q531" s="1" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="532" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54807,7 +54816,7 @@
         <v>20</v>
       </c>
       <c r="Q532" s="1" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="533" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54848,7 +54857,7 @@
         <v>20</v>
       </c>
       <c r="Q533" s="1" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="534" s="1" customFormat="1" ht="14.25" spans="1:17">
@@ -54889,7 +54898,7 @@
         <v>20</v>
       </c>
       <c r="Q534" s="1" t="s">
-        <v>1789</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="535" s="1" customFormat="1" ht="14.25" spans="1:17">
